--- a/Team-Data/2012-13/1-15-2012-13.xlsx
+++ b/Team-Data/2012-13/1-15-2012-13.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,7 +806,7 @@
         <v>-0.1</v>
       </c>
       <c r="AD2" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="AE2" t="n">
         <v>11</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>1-15-2012-13</t>
+          <t>2013-01-15</t>
         </is>
       </c>
     </row>
@@ -921,7 +988,7 @@
         <v>-0.4</v>
       </c>
       <c r="AD3" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="AE3" t="n">
         <v>15</v>
@@ -930,10 +997,10 @@
         <v>13</v>
       </c>
       <c r="AG3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AH3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI3" t="n">
         <v>14</v>
@@ -966,7 +1033,7 @@
         <v>28</v>
       </c>
       <c r="AS3" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AT3" t="n">
         <v>29</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>1-15-2012-13</t>
+          <t>2013-01-15</t>
         </is>
       </c>
     </row>
@@ -1025,28 +1092,28 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F4" t="n">
         <v>15</v>
       </c>
       <c r="G4" t="n">
-        <v>0.605</v>
+        <v>0.595</v>
       </c>
       <c r="H4" t="n">
         <v>48.7</v>
       </c>
       <c r="I4" t="n">
-        <v>35.4</v>
+        <v>35.2</v>
       </c>
       <c r="J4" t="n">
         <v>79.59999999999999</v>
       </c>
       <c r="K4" t="n">
-        <v>0.444</v>
+        <v>0.443</v>
       </c>
       <c r="L4" t="n">
         <v>7.5</v>
@@ -1058,55 +1125,55 @@
         <v>0.348</v>
       </c>
       <c r="O4" t="n">
-        <v>18.5</v>
+        <v>18.3</v>
       </c>
       <c r="P4" t="n">
-        <v>24.6</v>
+        <v>24.5</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.751</v>
+        <v>0.746</v>
       </c>
       <c r="R4" t="n">
         <v>12.6</v>
       </c>
       <c r="S4" t="n">
-        <v>29.4</v>
+        <v>29.6</v>
       </c>
       <c r="T4" t="n">
-        <v>42</v>
+        <v>42.2</v>
       </c>
       <c r="U4" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="V4" t="n">
-        <v>14.1</v>
+        <v>14.4</v>
       </c>
       <c r="W4" t="n">
         <v>7.2</v>
       </c>
       <c r="X4" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="Y4" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>18.6</v>
+        <v>18.5</v>
       </c>
       <c r="AA4" t="n">
         <v>21.4</v>
       </c>
       <c r="AB4" t="n">
-        <v>96.7</v>
+        <v>96.3</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AD4" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AE4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF4" t="n">
         <v>8</v>
@@ -1118,7 +1185,7 @@
         <v>6</v>
       </c>
       <c r="AI4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AJ4" t="n">
         <v>28</v>
@@ -1133,7 +1200,7 @@
         <v>9</v>
       </c>
       <c r="AN4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AO4" t="n">
         <v>7</v>
@@ -1142,28 +1209,28 @@
         <v>8</v>
       </c>
       <c r="AQ4" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AR4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AS4" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AT4" t="n">
         <v>15</v>
       </c>
       <c r="AU4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AV4" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AW4" t="n">
         <v>25</v>
       </c>
       <c r="AX4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AY4" t="n">
         <v>6</v>
@@ -1175,10 +1242,10 @@
         <v>5</v>
       </c>
       <c r="BB4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BC4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BD4" t="n">
         <v>10</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>1-15-2012-13</t>
+          <t>2013-01-15</t>
         </is>
       </c>
     </row>
@@ -1207,58 +1274,58 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E5" t="n">
         <v>9</v>
       </c>
       <c r="F5" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G5" t="n">
-        <v>0.237</v>
+        <v>0.243</v>
       </c>
       <c r="H5" t="n">
         <v>48.7</v>
       </c>
       <c r="I5" t="n">
-        <v>34.9</v>
+        <v>35.2</v>
       </c>
       <c r="J5" t="n">
-        <v>82.59999999999999</v>
+        <v>82.8</v>
       </c>
       <c r="K5" t="n">
-        <v>0.423</v>
+        <v>0.424</v>
       </c>
       <c r="L5" t="n">
         <v>5.8</v>
       </c>
       <c r="M5" t="n">
-        <v>16.6</v>
+        <v>16.8</v>
       </c>
       <c r="N5" t="n">
         <v>0.348</v>
       </c>
       <c r="O5" t="n">
-        <v>19.3</v>
+        <v>19.2</v>
       </c>
       <c r="P5" t="n">
-        <v>25.8</v>
+        <v>25.7</v>
       </c>
       <c r="Q5" t="n">
         <v>0.746</v>
       </c>
       <c r="R5" t="n">
-        <v>11.8</v>
+        <v>12.1</v>
       </c>
       <c r="S5" t="n">
-        <v>29.4</v>
+        <v>29.5</v>
       </c>
       <c r="T5" t="n">
-        <v>41.3</v>
+        <v>41.6</v>
       </c>
       <c r="U5" t="n">
-        <v>19.2</v>
+        <v>19.3</v>
       </c>
       <c r="V5" t="n">
         <v>14.2</v>
@@ -1267,31 +1334,31 @@
         <v>7.4</v>
       </c>
       <c r="X5" t="n">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="Y5" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="Z5" t="n">
-        <v>19.5</v>
+        <v>19.4</v>
       </c>
       <c r="AA5" t="n">
-        <v>21.6</v>
+        <v>21.5</v>
       </c>
       <c r="AB5" t="n">
-        <v>94.8</v>
+        <v>95.3</v>
       </c>
       <c r="AC5" t="n">
-        <v>-8.699999999999999</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="AD5" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AE5" t="n">
         <v>28</v>
       </c>
       <c r="AF5" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AG5" t="n">
         <v>28</v>
@@ -1315,34 +1382,34 @@
         <v>27</v>
       </c>
       <c r="AN5" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AO5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AP5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AQ5" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AR5" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AS5" t="n">
         <v>25</v>
       </c>
       <c r="AT5" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AU5" t="n">
         <v>30</v>
       </c>
       <c r="AV5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW5" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AX5" t="n">
         <v>6</v>
@@ -1351,13 +1418,13 @@
         <v>30</v>
       </c>
       <c r="AZ5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA5" t="n">
         <v>4</v>
       </c>
       <c r="BB5" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="BC5" t="n">
         <v>30</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>1-15-2012-13</t>
+          <t>2013-01-15</t>
         </is>
       </c>
     </row>
@@ -1467,7 +1534,7 @@
         <v>2.2</v>
       </c>
       <c r="AD6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AE6" t="n">
         <v>11</v>
@@ -1488,7 +1555,7 @@
         <v>25</v>
       </c>
       <c r="AK6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AL6" t="n">
         <v>30</v>
@@ -1497,7 +1564,7 @@
         <v>30</v>
       </c>
       <c r="AN6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AO6" t="n">
         <v>8</v>
@@ -1518,7 +1585,7 @@
         <v>7</v>
       </c>
       <c r="AU6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV6" t="n">
         <v>18</v>
@@ -1533,7 +1600,7 @@
         <v>20</v>
       </c>
       <c r="AZ6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA6" t="n">
         <v>11</v>
@@ -1542,7 +1609,7 @@
         <v>26</v>
       </c>
       <c r="BC6" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BD6" t="n">
         <v>10</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>1-15-2012-13</t>
+          <t>2013-01-15</t>
         </is>
       </c>
     </row>
@@ -1664,7 +1731,7 @@
         <v>25</v>
       </c>
       <c r="AI7" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AJ7" t="n">
         <v>3</v>
@@ -1679,7 +1746,7 @@
         <v>10</v>
       </c>
       <c r="AN7" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AO7" t="n">
         <v>21</v>
@@ -1697,7 +1764,7 @@
         <v>30</v>
       </c>
       <c r="AT7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AU7" t="n">
         <v>29</v>
@@ -1721,7 +1788,7 @@
         <v>12</v>
       </c>
       <c r="BB7" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BC7" t="n">
         <v>27</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>1-15-2012-13</t>
+          <t>2013-01-15</t>
         </is>
       </c>
     </row>
@@ -1831,16 +1898,16 @@
         <v>-3.2</v>
       </c>
       <c r="AD8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AE8" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AF8" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AG8" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AH8" t="n">
         <v>1</v>
@@ -1861,7 +1928,7 @@
         <v>13</v>
       </c>
       <c r="AN8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AO8" t="n">
         <v>15</v>
@@ -1876,13 +1943,13 @@
         <v>27</v>
       </c>
       <c r="AS8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AT8" t="n">
         <v>19</v>
       </c>
       <c r="AU8" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AV8" t="n">
         <v>14</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>1-15-2012-13</t>
+          <t>2013-01-15</t>
         </is>
       </c>
     </row>
@@ -1935,88 +2002,88 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E9" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F9" t="n">
         <v>16</v>
       </c>
       <c r="G9" t="n">
-        <v>0.6</v>
+        <v>0.59</v>
       </c>
       <c r="H9" t="n">
-        <v>48.4</v>
+        <v>48.3</v>
       </c>
       <c r="I9" t="n">
-        <v>39.6</v>
+        <v>39.4</v>
       </c>
       <c r="J9" t="n">
-        <v>85.3</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>0.465</v>
+        <v>0.464</v>
       </c>
       <c r="L9" t="n">
         <v>6.2</v>
       </c>
       <c r="M9" t="n">
-        <v>18.9</v>
+        <v>18.7</v>
       </c>
       <c r="N9" t="n">
-        <v>0.33</v>
+        <v>0.329</v>
       </c>
       <c r="O9" t="n">
-        <v>17.2</v>
+        <v>17.4</v>
       </c>
       <c r="P9" t="n">
-        <v>25.4</v>
+        <v>25.5</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.679</v>
+        <v>0.68</v>
       </c>
       <c r="R9" t="n">
-        <v>14.1</v>
+        <v>14.2</v>
       </c>
       <c r="S9" t="n">
-        <v>32.1</v>
+        <v>32.2</v>
       </c>
       <c r="T9" t="n">
-        <v>46.2</v>
+        <v>46.4</v>
       </c>
       <c r="U9" t="n">
-        <v>23.7</v>
+        <v>23.5</v>
       </c>
       <c r="V9" t="n">
-        <v>15.1</v>
+        <v>15.2</v>
       </c>
       <c r="W9" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="X9" t="n">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="Y9" t="n">
         <v>6.7</v>
       </c>
       <c r="Z9" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="AA9" t="n">
         <v>21.8</v>
       </c>
       <c r="AB9" t="n">
-        <v>102.7</v>
+        <v>102.4</v>
       </c>
       <c r="AC9" t="n">
         <v>3</v>
       </c>
       <c r="AD9" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AE9" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AF9" t="n">
         <v>11</v>
@@ -2025,7 +2092,7 @@
         <v>10</v>
       </c>
       <c r="AH9" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AI9" t="n">
         <v>2</v>
@@ -2040,16 +2107,16 @@
         <v>23</v>
       </c>
       <c r="AM9" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AN9" t="n">
         <v>28</v>
       </c>
       <c r="AO9" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AP9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AQ9" t="n">
         <v>30</v>
@@ -2061,16 +2128,16 @@
         <v>10</v>
       </c>
       <c r="AT9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU9" t="n">
         <v>3</v>
       </c>
       <c r="AV9" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AW9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AX9" t="n">
         <v>4</v>
@@ -2079,13 +2146,13 @@
         <v>28</v>
       </c>
       <c r="AZ9" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BA9" t="n">
         <v>3</v>
       </c>
       <c r="BB9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BC9" t="n">
         <v>7</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>1-15-2012-13</t>
+          <t>2013-01-15</t>
         </is>
       </c>
     </row>
@@ -2195,28 +2262,28 @@
         <v>-1.2</v>
       </c>
       <c r="AD10" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="AE10" t="n">
         <v>22</v>
       </c>
       <c r="AF10" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AG10" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AH10" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AI10" t="n">
         <v>21</v>
       </c>
       <c r="AJ10" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AK10" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AL10" t="n">
         <v>22</v>
@@ -2237,7 +2304,7 @@
         <v>27</v>
       </c>
       <c r="AR10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AS10" t="n">
         <v>13</v>
@@ -2246,7 +2313,7 @@
         <v>8</v>
       </c>
       <c r="AU10" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AV10" t="n">
         <v>24</v>
@@ -2267,10 +2334,10 @@
         <v>9</v>
       </c>
       <c r="BB10" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BC10" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BD10" t="n">
         <v>10</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>1-15-2012-13</t>
+          <t>2013-01-15</t>
         </is>
       </c>
     </row>
@@ -2377,10 +2444,10 @@
         <v>1.8</v>
       </c>
       <c r="AD11" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AE11" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AF11" t="n">
         <v>6</v>
@@ -2395,7 +2462,7 @@
         <v>6</v>
       </c>
       <c r="AJ11" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AK11" t="n">
         <v>8</v>
@@ -2452,7 +2519,7 @@
         <v>9</v>
       </c>
       <c r="BC11" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BD11" t="n">
         <v>10</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>1-15-2012-13</t>
+          <t>2013-01-15</t>
         </is>
       </c>
     </row>
@@ -2481,55 +2548,55 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E12" t="n">
         <v>21</v>
       </c>
       <c r="F12" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G12" t="n">
-        <v>0.538</v>
+        <v>0.553</v>
       </c>
       <c r="H12" t="n">
         <v>48.4</v>
       </c>
       <c r="I12" t="n">
-        <v>38.3</v>
+        <v>38.2</v>
       </c>
       <c r="J12" t="n">
-        <v>83.2</v>
+        <v>83.3</v>
       </c>
       <c r="K12" t="n">
-        <v>0.46</v>
+        <v>0.459</v>
       </c>
       <c r="L12" t="n">
-        <v>9.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="M12" t="n">
-        <v>28</v>
+        <v>27.7</v>
       </c>
       <c r="N12" t="n">
         <v>0.354</v>
       </c>
       <c r="O12" t="n">
-        <v>19.1</v>
+        <v>19.2</v>
       </c>
       <c r="P12" t="n">
         <v>25.5</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.749</v>
+        <v>0.754</v>
       </c>
       <c r="R12" t="n">
         <v>10.6</v>
       </c>
       <c r="S12" t="n">
-        <v>32.2</v>
+        <v>32.4</v>
       </c>
       <c r="T12" t="n">
-        <v>42.8</v>
+        <v>43</v>
       </c>
       <c r="U12" t="n">
         <v>22.8</v>
@@ -2541,43 +2608,43 @@
         <v>8.800000000000001</v>
       </c>
       <c r="X12" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="Y12" t="n">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="Z12" t="n">
-        <v>19.2</v>
+        <v>19.1</v>
       </c>
       <c r="AA12" t="n">
         <v>19.7</v>
       </c>
       <c r="AB12" t="n">
-        <v>105.5</v>
+        <v>105.4</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AD12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE12" t="n">
         <v>11</v>
       </c>
       <c r="AF12" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AG12" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AH12" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AI12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AJ12" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AK12" t="n">
         <v>7</v>
@@ -2589,28 +2656,28 @@
         <v>2</v>
       </c>
       <c r="AN12" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AO12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AP12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ12" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AR12" t="n">
         <v>23</v>
       </c>
       <c r="AS12" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AT12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AU12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AV12" t="n">
         <v>30</v>
@@ -2619,13 +2686,13 @@
         <v>3</v>
       </c>
       <c r="AX12" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AY12" t="n">
         <v>25</v>
       </c>
       <c r="AZ12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA12" t="n">
         <v>16</v>
@@ -2634,7 +2701,7 @@
         <v>1</v>
       </c>
       <c r="BC12" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>1-15-2012-13</t>
+          <t>2013-01-15</t>
         </is>
       </c>
     </row>
@@ -2663,16 +2730,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E13" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F13" t="n">
         <v>15</v>
       </c>
       <c r="G13" t="n">
-        <v>0.615</v>
+        <v>0.605</v>
       </c>
       <c r="H13" t="n">
         <v>48.4</v>
@@ -2681,7 +2748,7 @@
         <v>34.1</v>
       </c>
       <c r="J13" t="n">
-        <v>81.2</v>
+        <v>81</v>
       </c>
       <c r="K13" t="n">
         <v>0.42</v>
@@ -2693,58 +2760,58 @@
         <v>19.3</v>
       </c>
       <c r="N13" t="n">
-        <v>0.338</v>
+        <v>0.337</v>
       </c>
       <c r="O13" t="n">
-        <v>16.5</v>
+        <v>16.3</v>
       </c>
       <c r="P13" t="n">
-        <v>22.4</v>
+        <v>22.3</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.736</v>
+        <v>0.733</v>
       </c>
       <c r="R13" t="n">
-        <v>13.1</v>
+        <v>12.9</v>
       </c>
       <c r="S13" t="n">
-        <v>33.4</v>
+        <v>33.2</v>
       </c>
       <c r="T13" t="n">
-        <v>46.5</v>
+        <v>46.1</v>
       </c>
       <c r="U13" t="n">
-        <v>19.8</v>
+        <v>19.6</v>
       </c>
       <c r="V13" t="n">
         <v>14.9</v>
       </c>
       <c r="W13" t="n">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="X13" t="n">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="Y13" t="n">
         <v>5.6</v>
       </c>
       <c r="Z13" t="n">
-        <v>19.6</v>
+        <v>19.4</v>
       </c>
       <c r="AA13" t="n">
         <v>21.1</v>
       </c>
       <c r="AB13" t="n">
-        <v>91.3</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="AD13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE13" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AF13" t="n">
         <v>8</v>
@@ -2753,7 +2820,7 @@
         <v>8</v>
       </c>
       <c r="AH13" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AI13" t="n">
         <v>30</v>
@@ -2771,13 +2838,13 @@
         <v>16</v>
       </c>
       <c r="AN13" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AO13" t="n">
         <v>19</v>
       </c>
       <c r="AP13" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AQ13" t="n">
         <v>24</v>
@@ -2786,10 +2853,10 @@
         <v>5</v>
       </c>
       <c r="AS13" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT13" t="n">
         <v>2</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>1</v>
       </c>
       <c r="AU13" t="n">
         <v>28</v>
@@ -2816,7 +2883,7 @@
         <v>29</v>
       </c>
       <c r="BC13" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="BD13" t="n">
         <v>10</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>1-15-2012-13</t>
+          <t>2013-01-15</t>
         </is>
       </c>
     </row>
@@ -2845,88 +2912,88 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E14" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F14" t="n">
         <v>9</v>
       </c>
       <c r="G14" t="n">
-        <v>0.769</v>
+        <v>0.763</v>
       </c>
       <c r="H14" t="n">
         <v>48.1</v>
       </c>
       <c r="I14" t="n">
-        <v>38.7</v>
+        <v>38.6</v>
       </c>
       <c r="J14" t="n">
         <v>80.90000000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>0.478</v>
+        <v>0.477</v>
       </c>
       <c r="L14" t="n">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="M14" t="n">
         <v>20.6</v>
       </c>
       <c r="N14" t="n">
-        <v>0.355</v>
+        <v>0.35</v>
       </c>
       <c r="O14" t="n">
-        <v>17.5</v>
+        <v>17.4</v>
       </c>
       <c r="P14" t="n">
-        <v>24.4</v>
+        <v>24.3</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.718</v>
+        <v>0.714</v>
       </c>
       <c r="R14" t="n">
-        <v>11.3</v>
+        <v>11.4</v>
       </c>
       <c r="S14" t="n">
-        <v>30.3</v>
+        <v>30.5</v>
       </c>
       <c r="T14" t="n">
-        <v>41.7</v>
+        <v>41.8</v>
       </c>
       <c r="U14" t="n">
         <v>23.8</v>
       </c>
       <c r="V14" t="n">
-        <v>14.4</v>
+        <v>14.3</v>
       </c>
       <c r="W14" t="n">
-        <v>10.5</v>
+        <v>10.6</v>
       </c>
       <c r="X14" t="n">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="Y14" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="Z14" t="n">
         <v>20.9</v>
       </c>
       <c r="AA14" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="AB14" t="n">
-        <v>102.1</v>
+        <v>101.7</v>
       </c>
       <c r="AC14" t="n">
         <v>8.9</v>
       </c>
       <c r="AD14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF14" t="n">
         <v>2</v>
@@ -2941,7 +3008,7 @@
         <v>3</v>
       </c>
       <c r="AJ14" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AK14" t="n">
         <v>4</v>
@@ -2953,10 +3020,10 @@
         <v>11</v>
       </c>
       <c r="AN14" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AO14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AP14" t="n">
         <v>9</v>
@@ -2965,28 +3032,28 @@
         <v>26</v>
       </c>
       <c r="AR14" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AS14" t="n">
         <v>18</v>
       </c>
       <c r="AT14" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AU14" t="n">
         <v>2</v>
       </c>
       <c r="AV14" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="AW14" t="n">
         <v>1</v>
       </c>
       <c r="AX14" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AY14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AZ14" t="n">
         <v>22</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>1-15-2012-13</t>
+          <t>2013-01-15</t>
         </is>
       </c>
     </row>
@@ -3027,61 +3094,61 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E15" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F15" t="n">
         <v>21</v>
       </c>
       <c r="G15" t="n">
-        <v>0.447</v>
+        <v>0.432</v>
       </c>
       <c r="H15" t="n">
         <v>48.1</v>
       </c>
       <c r="I15" t="n">
-        <v>37.4</v>
+        <v>37.3</v>
       </c>
       <c r="J15" t="n">
         <v>81.90000000000001</v>
       </c>
       <c r="K15" t="n">
-        <v>0.456</v>
+        <v>0.455</v>
       </c>
       <c r="L15" t="n">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="M15" t="n">
-        <v>25.3</v>
+        <v>25.2</v>
       </c>
       <c r="N15" t="n">
         <v>0.355</v>
       </c>
       <c r="O15" t="n">
-        <v>19.7</v>
+        <v>19.9</v>
       </c>
       <c r="P15" t="n">
-        <v>28.4</v>
+        <v>28.7</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.695</v>
       </c>
       <c r="R15" t="n">
-        <v>12.5</v>
+        <v>12.6</v>
       </c>
       <c r="S15" t="n">
-        <v>32.8</v>
+        <v>32.7</v>
       </c>
       <c r="T15" t="n">
         <v>45.3</v>
       </c>
       <c r="U15" t="n">
-        <v>22.1</v>
+        <v>21.9</v>
       </c>
       <c r="V15" t="n">
-        <v>15.3</v>
+        <v>15.4</v>
       </c>
       <c r="W15" t="n">
         <v>7.6</v>
@@ -3093,19 +3160,19 @@
         <v>5</v>
       </c>
       <c r="Z15" t="n">
-        <v>19.2</v>
+        <v>19.1</v>
       </c>
       <c r="AA15" t="n">
-        <v>23.1</v>
+        <v>23.3</v>
       </c>
       <c r="AB15" t="n">
         <v>103.4</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="AD15" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AE15" t="n">
         <v>18</v>
@@ -3117,7 +3184,7 @@
         <v>19</v>
       </c>
       <c r="AH15" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AI15" t="n">
         <v>11</v>
@@ -3126,7 +3193,7 @@
         <v>18</v>
       </c>
       <c r="AK15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AL15" t="n">
         <v>3</v>
@@ -3135,7 +3202,7 @@
         <v>3</v>
       </c>
       <c r="AN15" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AO15" t="n">
         <v>2</v>
@@ -3147,7 +3214,7 @@
         <v>29</v>
       </c>
       <c r="AR15" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AS15" t="n">
         <v>5</v>
@@ -3156,7 +3223,7 @@
         <v>3</v>
       </c>
       <c r="AU15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AV15" t="n">
         <v>26</v>
@@ -3165,13 +3232,13 @@
         <v>18</v>
       </c>
       <c r="AX15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AY15" t="n">
         <v>14</v>
       </c>
       <c r="AZ15" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA15" t="n">
         <v>1</v>
@@ -3180,7 +3247,7 @@
         <v>4</v>
       </c>
       <c r="BC15" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BD15" t="n">
         <v>10</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>1-15-2012-13</t>
+          <t>2013-01-15</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3354,7 @@
         <v>4</v>
       </c>
       <c r="AD16" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AE16" t="n">
         <v>4</v>
@@ -3332,10 +3399,10 @@
         <v>3</v>
       </c>
       <c r="AS16" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AT16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AU16" t="n">
         <v>22</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>1-15-2012-13</t>
+          <t>2013-01-15</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3536,7 @@
         <v>5</v>
       </c>
       <c r="AD17" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AE17" t="n">
         <v>4</v>
@@ -3484,7 +3551,7 @@
         <v>13</v>
       </c>
       <c r="AI17" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AJ17" t="n">
         <v>30</v>
@@ -3502,7 +3569,7 @@
         <v>1</v>
       </c>
       <c r="AO17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AP17" t="n">
         <v>12</v>
@@ -3514,19 +3581,19 @@
         <v>30</v>
       </c>
       <c r="AS17" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AT17" t="n">
         <v>30</v>
       </c>
       <c r="AU17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AV17" t="n">
         <v>4</v>
       </c>
       <c r="AW17" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AX17" t="n">
         <v>17</v>
@@ -3535,13 +3602,13 @@
         <v>1</v>
       </c>
       <c r="AZ17" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="BA17" t="n">
         <v>14</v>
       </c>
       <c r="BB17" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BC17" t="n">
         <v>4</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>1-15-2012-13</t>
+          <t>2013-01-15</t>
         </is>
       </c>
     </row>
@@ -3573,115 +3640,115 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E18" t="n">
         <v>19</v>
       </c>
       <c r="F18" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G18" t="n">
-        <v>0.514</v>
+        <v>0.528</v>
       </c>
       <c r="H18" t="n">
         <v>48.3</v>
       </c>
       <c r="I18" t="n">
-        <v>37.1</v>
+        <v>37.2</v>
       </c>
       <c r="J18" t="n">
-        <v>85.90000000000001</v>
+        <v>85.7</v>
       </c>
       <c r="K18" t="n">
-        <v>0.432</v>
+        <v>0.435</v>
       </c>
       <c r="L18" t="n">
         <v>6.1</v>
       </c>
       <c r="M18" t="n">
-        <v>18.1</v>
+        <v>17.8</v>
       </c>
       <c r="N18" t="n">
-        <v>0.336</v>
+        <v>0.34</v>
       </c>
       <c r="O18" t="n">
-        <v>15.9</v>
+        <v>16</v>
       </c>
       <c r="P18" t="n">
         <v>21.4</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.746</v>
+        <v>0.75</v>
       </c>
       <c r="R18" t="n">
-        <v>12.8</v>
+        <v>12.6</v>
       </c>
       <c r="S18" t="n">
         <v>30.6</v>
       </c>
       <c r="T18" t="n">
-        <v>43.5</v>
+        <v>43.2</v>
       </c>
       <c r="U18" t="n">
-        <v>21.7</v>
+        <v>21.9</v>
       </c>
       <c r="V18" t="n">
         <v>14.4</v>
       </c>
       <c r="W18" t="n">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="X18" t="n">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="Y18" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="Z18" t="n">
-        <v>19.2</v>
+        <v>19.4</v>
       </c>
       <c r="AA18" t="n">
         <v>19.5</v>
       </c>
       <c r="AB18" t="n">
-        <v>96.3</v>
+        <v>96.5</v>
       </c>
       <c r="AC18" t="n">
-        <v>-1.2</v>
+        <v>-0.8</v>
       </c>
       <c r="AD18" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AE18" t="n">
         <v>17</v>
       </c>
       <c r="AF18" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AG18" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AH18" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI18" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AJ18" t="n">
         <v>1</v>
       </c>
       <c r="AK18" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL18" t="n">
         <v>25</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>24</v>
       </c>
       <c r="AM18" t="n">
         <v>24</v>
       </c>
       <c r="AN18" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AO18" t="n">
         <v>23</v>
@@ -3690,22 +3757,22 @@
         <v>18</v>
       </c>
       <c r="AQ18" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AR18" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AS18" t="n">
+        <v>16</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU18" t="n">
         <v>15</v>
       </c>
-      <c r="AT18" t="n">
-        <v>9</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>19</v>
-      </c>
       <c r="AV18" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AW18" t="n">
         <v>6</v>
@@ -3714,19 +3781,19 @@
         <v>1</v>
       </c>
       <c r="AY18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AZ18" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BA18" t="n">
         <v>18</v>
       </c>
       <c r="BB18" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BC18" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BD18" t="n">
         <v>10</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>1-15-2012-13</t>
+          <t>2013-01-15</t>
         </is>
       </c>
     </row>
@@ -3836,7 +3903,7 @@
         <v>29</v>
       </c>
       <c r="AE19" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AF19" t="n">
         <v>17</v>
@@ -3848,7 +3915,7 @@
         <v>26</v>
       </c>
       <c r="AI19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AJ19" t="n">
         <v>16</v>
@@ -3860,7 +3927,7 @@
         <v>27</v>
       </c>
       <c r="AM19" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AN19" t="n">
         <v>30</v>
@@ -3869,7 +3936,7 @@
         <v>5</v>
       </c>
       <c r="AP19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AQ19" t="n">
         <v>23</v>
@@ -3884,7 +3951,7 @@
         <v>4</v>
       </c>
       <c r="AU19" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AV19" t="n">
         <v>25</v>
@@ -3905,7 +3972,7 @@
         <v>2</v>
       </c>
       <c r="BB19" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BC19" t="n">
         <v>19</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>1-15-2012-13</t>
+          <t>2013-01-15</t>
         </is>
       </c>
     </row>
@@ -3937,55 +4004,55 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E20" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F20" t="n">
         <v>26</v>
       </c>
       <c r="G20" t="n">
-        <v>0.316</v>
+        <v>0.297</v>
       </c>
       <c r="H20" t="n">
         <v>48.5</v>
       </c>
       <c r="I20" t="n">
-        <v>35.7</v>
+        <v>35.5</v>
       </c>
       <c r="J20" t="n">
         <v>80.2</v>
       </c>
       <c r="K20" t="n">
-        <v>0.445</v>
+        <v>0.443</v>
       </c>
       <c r="L20" t="n">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="M20" t="n">
         <v>18.6</v>
       </c>
       <c r="N20" t="n">
-        <v>0.373</v>
+        <v>0.368</v>
       </c>
       <c r="O20" t="n">
-        <v>14</v>
+        <v>14.1</v>
       </c>
       <c r="P20" t="n">
         <v>18.1</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.776</v>
+        <v>0.777</v>
       </c>
       <c r="R20" t="n">
-        <v>11.4</v>
+        <v>11.3</v>
       </c>
       <c r="S20" t="n">
-        <v>30.2</v>
+        <v>30.1</v>
       </c>
       <c r="T20" t="n">
-        <v>41.5</v>
+        <v>41.4</v>
       </c>
       <c r="U20" t="n">
         <v>21.2</v>
@@ -3994,28 +4061,28 @@
         <v>14.4</v>
       </c>
       <c r="W20" t="n">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="X20" t="n">
         <v>5.4</v>
       </c>
       <c r="Y20" t="n">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="Z20" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="AA20" t="n">
-        <v>18.4</v>
+        <v>18.3</v>
       </c>
       <c r="AB20" t="n">
-        <v>92.40000000000001</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="AC20" t="n">
-        <v>-4.4</v>
+        <v>-4.9</v>
       </c>
       <c r="AD20" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AE20" t="n">
         <v>27</v>
@@ -4027,25 +4094,25 @@
         <v>27</v>
       </c>
       <c r="AH20" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AI20" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AJ20" t="n">
         <v>26</v>
       </c>
       <c r="AK20" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="AL20" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AM20" t="n">
         <v>21</v>
       </c>
       <c r="AN20" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AO20" t="n">
         <v>27</v>
@@ -4054,22 +4121,22 @@
         <v>28</v>
       </c>
       <c r="AQ20" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AR20" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AS20" t="n">
         <v>20</v>
       </c>
       <c r="AT20" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AU20" t="n">
         <v>20</v>
       </c>
       <c r="AV20" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AW20" t="n">
         <v>28</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>1-15-2012-13</t>
+          <t>2013-01-15</t>
         </is>
       </c>
     </row>
@@ -4197,7 +4264,7 @@
         <v>4.7</v>
       </c>
       <c r="AD21" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="AE21" t="n">
         <v>4</v>
@@ -4212,13 +4279,13 @@
         <v>28</v>
       </c>
       <c r="AI21" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AJ21" t="n">
         <v>5</v>
       </c>
       <c r="AK21" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AL21" t="n">
         <v>1</v>
@@ -4242,7 +4309,7 @@
         <v>20</v>
       </c>
       <c r="AS21" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AT21" t="n">
         <v>27</v>
@@ -4257,7 +4324,7 @@
         <v>8</v>
       </c>
       <c r="AX21" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AY21" t="n">
         <v>2</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>1-15-2012-13</t>
+          <t>2013-01-15</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4446,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AD22" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="AE22" t="n">
         <v>1</v>
@@ -4427,7 +4494,7 @@
         <v>4</v>
       </c>
       <c r="AT22" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AU22" t="n">
         <v>18</v>
@@ -4445,7 +4512,7 @@
         <v>3</v>
       </c>
       <c r="AZ22" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BA22" t="n">
         <v>10</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>1-15-2012-13</t>
+          <t>2013-01-15</t>
         </is>
       </c>
     </row>
@@ -4561,13 +4628,13 @@
         <v>-3.6</v>
       </c>
       <c r="AD23" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="AE23" t="n">
         <v>25</v>
       </c>
       <c r="AF23" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AG23" t="n">
         <v>25</v>
@@ -4582,13 +4649,13 @@
         <v>13</v>
       </c>
       <c r="AK23" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AL23" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AM23" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AN23" t="n">
         <v>20</v>
@@ -4606,7 +4673,7 @@
         <v>24</v>
       </c>
       <c r="AS23" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AT23" t="n">
         <v>13</v>
@@ -4627,13 +4694,13 @@
         <v>10</v>
       </c>
       <c r="AZ23" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BA23" t="n">
         <v>30</v>
       </c>
       <c r="BB23" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BC23" t="n">
         <v>23</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>1-15-2012-13</t>
+          <t>2013-01-15</t>
         </is>
       </c>
     </row>
@@ -4665,43 +4732,43 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E24" t="n">
         <v>16</v>
       </c>
       <c r="F24" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G24" t="n">
-        <v>0.41</v>
+        <v>0.421</v>
       </c>
       <c r="H24" t="n">
         <v>48.3</v>
       </c>
       <c r="I24" t="n">
-        <v>36.8</v>
+        <v>36.7</v>
       </c>
       <c r="J24" t="n">
-        <v>83.59999999999999</v>
+        <v>83.7</v>
       </c>
       <c r="K24" t="n">
-        <v>0.44</v>
+        <v>0.439</v>
       </c>
       <c r="L24" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="M24" t="n">
-        <v>18.2</v>
+        <v>18.1</v>
       </c>
       <c r="N24" t="n">
-        <v>0.361</v>
+        <v>0.356</v>
       </c>
       <c r="O24" t="n">
-        <v>12.6</v>
+        <v>12.7</v>
       </c>
       <c r="P24" t="n">
-        <v>17.5</v>
+        <v>17.6</v>
       </c>
       <c r="Q24" t="n">
         <v>0.722</v>
@@ -4710,22 +4777,22 @@
         <v>10.8</v>
       </c>
       <c r="S24" t="n">
-        <v>30.3</v>
+        <v>30.6</v>
       </c>
       <c r="T24" t="n">
-        <v>41.2</v>
+        <v>41.4</v>
       </c>
       <c r="U24" t="n">
-        <v>21.8</v>
+        <v>21.6</v>
       </c>
       <c r="V24" t="n">
         <v>12.8</v>
       </c>
       <c r="W24" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="X24" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="Y24" t="n">
         <v>4.6</v>
@@ -4737,16 +4804,16 @@
         <v>17</v>
       </c>
       <c r="AB24" t="n">
-        <v>92.8</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="AC24" t="n">
-        <v>-4.4</v>
+        <v>-4.2</v>
       </c>
       <c r="AD24" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE24" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AF24" t="n">
         <v>20</v>
@@ -4755,7 +4822,7 @@
         <v>20</v>
       </c>
       <c r="AH24" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI24" t="n">
         <v>15</v>
@@ -4764,16 +4831,16 @@
         <v>7</v>
       </c>
       <c r="AK24" t="n">
+        <v>21</v>
+      </c>
+      <c r="AL24" t="n">
         <v>20</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>17</v>
       </c>
       <c r="AM24" t="n">
         <v>23</v>
       </c>
       <c r="AN24" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AO24" t="n">
         <v>30</v>
@@ -4788,25 +4855,25 @@
         <v>21</v>
       </c>
       <c r="AS24" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AT24" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AU24" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AV24" t="n">
         <v>3</v>
       </c>
       <c r="AW24" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AX24" t="n">
         <v>18</v>
       </c>
       <c r="AY24" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ24" t="n">
         <v>6</v>
@@ -4818,7 +4885,7 @@
         <v>27</v>
       </c>
       <c r="BC24" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BD24" t="n">
         <v>10</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>1-15-2012-13</t>
+          <t>2013-01-15</t>
         </is>
       </c>
     </row>
@@ -4946,10 +5013,10 @@
         <v>4</v>
       </c>
       <c r="AK25" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AL25" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AM25" t="n">
         <v>22</v>
@@ -4976,7 +5043,7 @@
         <v>24</v>
       </c>
       <c r="AU25" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AV25" t="n">
         <v>5</v>
@@ -5000,7 +5067,7 @@
         <v>19</v>
       </c>
       <c r="BC25" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BD25" t="n">
         <v>10</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>1-15-2012-13</t>
+          <t>2013-01-15</t>
         </is>
       </c>
     </row>
@@ -5029,94 +5096,94 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E26" t="n">
         <v>20</v>
       </c>
       <c r="F26" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G26" t="n">
-        <v>0.526</v>
+        <v>0.541</v>
       </c>
       <c r="H26" t="n">
-        <v>48.9</v>
+        <v>48.8</v>
       </c>
       <c r="I26" t="n">
-        <v>36.3</v>
+        <v>36.1</v>
       </c>
       <c r="J26" t="n">
-        <v>83.3</v>
+        <v>83.2</v>
       </c>
       <c r="K26" t="n">
-        <v>0.435</v>
+        <v>0.434</v>
       </c>
       <c r="L26" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="M26" t="n">
-        <v>24.4</v>
+        <v>24.3</v>
       </c>
       <c r="N26" t="n">
-        <v>0.341</v>
+        <v>0.342</v>
       </c>
       <c r="O26" t="n">
-        <v>16.3</v>
+        <v>16.2</v>
       </c>
       <c r="P26" t="n">
         <v>21.1</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.771</v>
+        <v>0.769</v>
       </c>
       <c r="R26" t="n">
-        <v>11.9</v>
+        <v>12</v>
       </c>
       <c r="S26" t="n">
-        <v>29.9</v>
+        <v>29.7</v>
       </c>
       <c r="T26" t="n">
-        <v>41.8</v>
+        <v>41.7</v>
       </c>
       <c r="U26" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="V26" t="n">
-        <v>14.6</v>
+        <v>14.5</v>
       </c>
       <c r="W26" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="X26" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="Y26" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="Z26" t="n">
-        <v>18.9</v>
+        <v>18.8</v>
       </c>
       <c r="AA26" t="n">
-        <v>19.1</v>
+        <v>19</v>
       </c>
       <c r="AB26" t="n">
-        <v>97.09999999999999</v>
+        <v>96.8</v>
       </c>
       <c r="AC26" t="n">
-        <v>-2.1</v>
+        <v>-2</v>
       </c>
       <c r="AD26" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AE26" t="n">
         <v>15</v>
       </c>
       <c r="AF26" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG26" t="n">
         <v>14</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>15</v>
       </c>
       <c r="AH26" t="n">
         <v>3</v>
@@ -5125,10 +5192,10 @@
         <v>19</v>
       </c>
       <c r="AJ26" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AK26" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AL26" t="n">
         <v>7</v>
@@ -5137,7 +5204,7 @@
         <v>4</v>
       </c>
       <c r="AN26" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AO26" t="n">
         <v>20</v>
@@ -5149,13 +5216,13 @@
         <v>12</v>
       </c>
       <c r="AR26" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AS26" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AT26" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AU26" t="n">
         <v>23</v>
@@ -5167,10 +5234,10 @@
         <v>19</v>
       </c>
       <c r="AX26" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AY26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AZ26" t="n">
         <v>5</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>1-15-2012-13</t>
+          <t>2013-01-15</t>
         </is>
       </c>
     </row>
@@ -5289,16 +5356,16 @@
         <v>-5.9</v>
       </c>
       <c r="AD27" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="AE27" t="n">
         <v>22</v>
       </c>
       <c r="AF27" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AG27" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AH27" t="n">
         <v>16</v>
@@ -5307,22 +5374,22 @@
         <v>17</v>
       </c>
       <c r="AJ27" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AK27" t="n">
         <v>19</v>
       </c>
       <c r="AL27" t="n">
+        <v>15</v>
+      </c>
+      <c r="AM27" t="n">
         <v>16</v>
       </c>
-      <c r="AM27" t="n">
-        <v>17</v>
-      </c>
       <c r="AN27" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AO27" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AP27" t="n">
         <v>13</v>
@@ -5331,7 +5398,7 @@
         <v>11</v>
       </c>
       <c r="AR27" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AS27" t="n">
         <v>29</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>1-15-2012-13</t>
+          <t>2013-01-15</t>
         </is>
       </c>
     </row>
@@ -5474,7 +5541,7 @@
         <v>1</v>
       </c>
       <c r="AE28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF28" t="n">
         <v>3</v>
@@ -5516,10 +5583,10 @@
         <v>29</v>
       </c>
       <c r="AS28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AT28" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AU28" t="n">
         <v>1</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>1-15-2012-13</t>
+          <t>2013-01-15</t>
         </is>
       </c>
     </row>
@@ -5575,37 +5642,37 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E29" t="n">
         <v>14</v>
       </c>
       <c r="F29" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G29" t="n">
-        <v>0.368</v>
+        <v>0.378</v>
       </c>
       <c r="H29" t="n">
         <v>48.8</v>
       </c>
       <c r="I29" t="n">
-        <v>35.9</v>
+        <v>35.8</v>
       </c>
       <c r="J29" t="n">
         <v>82</v>
       </c>
       <c r="K29" t="n">
-        <v>0.438</v>
+        <v>0.437</v>
       </c>
       <c r="L29" t="n">
         <v>7.6</v>
       </c>
       <c r="M29" t="n">
-        <v>22</v>
+        <v>22.2</v>
       </c>
       <c r="N29" t="n">
-        <v>0.345</v>
+        <v>0.342</v>
       </c>
       <c r="O29" t="n">
         <v>17.4</v>
@@ -5614,7 +5681,7 @@
         <v>22.4</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.777</v>
+        <v>0.775</v>
       </c>
       <c r="R29" t="n">
         <v>10.8</v>
@@ -5626,16 +5693,16 @@
         <v>40</v>
       </c>
       <c r="U29" t="n">
-        <v>22.3</v>
+        <v>22.4</v>
       </c>
       <c r="V29" t="n">
         <v>12.7</v>
       </c>
       <c r="W29" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="X29" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="Y29" t="n">
         <v>5.3</v>
@@ -5644,28 +5711,28 @@
         <v>22.8</v>
       </c>
       <c r="AA29" t="n">
-        <v>19.5</v>
+        <v>19.4</v>
       </c>
       <c r="AB29" t="n">
-        <v>96.8</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="AC29" t="n">
-        <v>-1.9</v>
+        <v>-1.8</v>
       </c>
       <c r="AD29" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AE29" t="n">
         <v>22</v>
       </c>
       <c r="AF29" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AG29" t="n">
         <v>22</v>
       </c>
       <c r="AH29" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AI29" t="n">
         <v>22</v>
@@ -5683,16 +5750,16 @@
         <v>7</v>
       </c>
       <c r="AN29" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AO29" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AP29" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AQ29" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AR29" t="n">
         <v>22</v>
@@ -5704,13 +5771,13 @@
         <v>28</v>
       </c>
       <c r="AU29" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AV29" t="n">
         <v>2</v>
       </c>
       <c r="AW29" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AX29" t="n">
         <v>24</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>1-15-2012-13</t>
+          <t>2013-01-15</t>
         </is>
       </c>
     </row>
@@ -5844,7 +5911,7 @@
         <v>17</v>
       </c>
       <c r="AG30" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AH30" t="n">
         <v>20</v>
@@ -5859,13 +5926,13 @@
         <v>13</v>
       </c>
       <c r="AL30" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AM30" t="n">
         <v>25</v>
       </c>
       <c r="AN30" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AO30" t="n">
         <v>6</v>
@@ -5877,25 +5944,25 @@
         <v>13</v>
       </c>
       <c r="AR30" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AS30" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AT30" t="n">
         <v>14</v>
       </c>
       <c r="AU30" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AV30" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AW30" t="n">
         <v>9</v>
       </c>
       <c r="AX30" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AY30" t="n">
         <v>23</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>1-15-2012-13</t>
+          <t>2013-01-15</t>
         </is>
       </c>
     </row>
@@ -6056,7 +6123,7 @@
         <v>25</v>
       </c>
       <c r="AQ31" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AR31" t="n">
         <v>17</v>
@@ -6071,10 +6138,10 @@
         <v>21</v>
       </c>
       <c r="AV31" t="n">
+        <v>21</v>
+      </c>
+      <c r="AW31" t="n">
         <v>22</v>
-      </c>
-      <c r="AW31" t="n">
-        <v>20</v>
       </c>
       <c r="AX31" t="n">
         <v>23</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>1-15-2012-13</t>
+          <t>2013-01-15</t>
         </is>
       </c>
     </row>
